--- a/outputs/Block5B_Senate_Competitive_Races.xlsx
+++ b/outputs/Block5B_Senate_Competitive_Races.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="87">
   <si>
     <t>STATE</t>
   </si>
@@ -127,6 +127,36 @@
     <t>Model Disagreement PP</t>
   </si>
   <si>
+    <t>Cook PVI</t>
+  </si>
+  <si>
+    <t>PVI D-Signed</t>
+  </si>
+  <si>
+    <t>Last Election Raw</t>
+  </si>
+  <si>
+    <t>Last Election Party</t>
+  </si>
+  <si>
+    <t>Last Election Vote Share</t>
+  </si>
+  <si>
+    <t>Prior Senate Margin D-Signed PP</t>
+  </si>
+  <si>
+    <t>Model vs PVI Disagreement PP</t>
+  </si>
+  <si>
+    <t>Model vs Prior Result Disagreement PP</t>
+  </si>
+  <si>
+    <t>Structural Disagreement PP</t>
+  </si>
+  <si>
+    <t>Structural Uncertainty Add-on PP</t>
+  </si>
+  <si>
     <t>State Idiosyncratic Sigma PP</t>
   </si>
   <si>
@@ -160,67 +190,91 @@
     <t>Mean Comparability Weight</t>
   </si>
   <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
     <t>Maine</t>
   </si>
   <si>
-    <t>Michigan</t>
-  </si>
-  <si>
-    <t>Ohio</t>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>Texas</t>
   </si>
   <si>
     <t>Iowa</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Texas</t>
+    <t>D</t>
   </si>
   <si>
     <t>R</t>
   </si>
   <si>
-    <t>D</t>
+    <t>DSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
     <t>RSenLeanPollLD (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>DSenLeanPollH (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
     <t>RSenLeanPollH (&gt;1&lt;=5%)</t>
   </si>
   <si>
-    <t>RSenTosPoll (&lt;=1%)</t>
-  </si>
-  <si>
     <t>D Lean</t>
   </si>
   <si>
     <t>R Lean</t>
   </si>
   <si>
+    <t>Lean</t>
+  </si>
+  <si>
     <t>Toss-Up</t>
   </si>
   <si>
-    <t>Lean</t>
+    <t>Democratic Hold</t>
   </si>
   <si>
     <t>Democratic Flip</t>
   </si>
   <si>
-    <t>Republican Flip</t>
-  </si>
-  <si>
     <t>Republican Hold</t>
   </si>
   <si>
-    <t>Democratic Hold</t>
-  </si>
-  <si>
     <t>Polling-error correction retained — inner LOEO improved MAE</t>
+  </si>
+  <si>
+    <t>EVEN</t>
+  </si>
+  <si>
+    <t>R+5</t>
+  </si>
+  <si>
+    <t>D+4</t>
+  </si>
+  <si>
+    <t>R+6</t>
+  </si>
+  <si>
+    <t>49.90% D</t>
+  </si>
+  <si>
+    <t>Appointed (2025)[p]</t>
+  </si>
+  <si>
+    <t>50.98% R</t>
+  </si>
+  <si>
+    <t>53.90% R</t>
+  </si>
+  <si>
+    <t>53.51% R</t>
+  </si>
+  <si>
+    <t>51.74% R</t>
   </si>
 </sst>
 </file>
@@ -578,10 +632,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AV7"/>
+  <dimension ref="A1:BF7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:48">
+    <row r="1" spans="1:58">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -726,49 +780,79 @@
       <c r="AV1" s="1" t="s">
         <v>47</v>
       </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
-    <row r="2" spans="1:48">
+    <row r="2" spans="1:58">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C2">
-        <v>49.25</v>
+        <v>47.92</v>
       </c>
       <c r="D2">
-        <v>47.1</v>
+        <v>44.95</v>
       </c>
       <c r="E2">
-        <v>2.15</v>
+        <v>2.97</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="G2" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I2">
-        <v>51.12</v>
+        <v>51.6</v>
       </c>
       <c r="J2">
-        <v>48.88</v>
+        <v>48.4</v>
       </c>
       <c r="K2">
-        <v>2.23</v>
+        <v>3.2</v>
       </c>
       <c r="L2">
-        <v>-1.89</v>
+        <v>0.12</v>
       </c>
       <c r="M2">
-        <v>0.34</v>
+        <v>3.32</v>
       </c>
       <c r="N2">
-        <v>0.34</v>
+        <v>3.32</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -777,144 +861,174 @@
         <v>1</v>
       </c>
       <c r="Q2">
-        <v>50.17</v>
+        <v>51.66</v>
       </c>
       <c r="R2">
-        <v>49.83</v>
+        <v>48.34</v>
       </c>
       <c r="S2">
-        <v>-1.89</v>
+        <v>0.12</v>
       </c>
       <c r="T2">
+        <v>3.32</v>
+      </c>
+      <c r="U2">
+        <v>3.32</v>
+      </c>
+      <c r="V2">
+        <v>69.5</v>
+      </c>
+      <c r="W2">
+        <v>30.5</v>
+      </c>
+      <c r="X2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC2">
+        <v>30.5</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE2">
+        <v>7.27</v>
+      </c>
+      <c r="AF2">
         <v>0.34</v>
       </c>
-      <c r="U2">
-        <v>0.34</v>
-      </c>
-      <c r="V2">
-        <v>51.82</v>
-      </c>
-      <c r="W2">
-        <v>48.18</v>
-      </c>
-      <c r="X2" t="s">
-        <v>62</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AG2">
+        <v>2.9</v>
+      </c>
+      <c r="AH2">
+        <v>2.56</v>
+      </c>
+      <c r="AI2">
+        <v>3.24</v>
+      </c>
+      <c r="AJ2">
+        <v>-0.34</v>
+      </c>
+      <c r="AK2">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AM2">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AO2" t="s">
         <v>64</v>
       </c>
-      <c r="AA2" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC2">
-        <v>51.82</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE2">
-        <v>4.93</v>
-      </c>
-      <c r="AF2">
-        <v>0.92</v>
-      </c>
-      <c r="AG2">
-        <v>2.53</v>
-      </c>
-      <c r="AH2">
-        <v>1.61</v>
-      </c>
-      <c r="AI2">
-        <v>3.46</v>
-      </c>
-      <c r="AJ2">
-        <v>2.53</v>
-      </c>
-      <c r="AK2">
-        <v>0</v>
-      </c>
-      <c r="AL2">
-        <v>6.17</v>
-      </c>
-      <c r="AM2">
-        <v>6.85</v>
-      </c>
-      <c r="AN2">
-        <v>7.52</v>
-      </c>
-      <c r="AO2">
+      <c r="AP2">
+        <v>0.499</v>
+      </c>
+      <c r="AQ2">
+        <v>-0.2000000000000028</v>
+      </c>
+      <c r="AR2">
+        <v>3.322364192499973</v>
+      </c>
+      <c r="AS2">
+        <v>3.522364192499976</v>
+      </c>
+      <c r="AT2">
+        <v>3.422364192499974</v>
+      </c>
+      <c r="AU2">
+        <v>0.8555910481249935</v>
+      </c>
+      <c r="AV2">
+        <v>4.72</v>
+      </c>
+      <c r="AW2">
+        <v>5.73</v>
+      </c>
+      <c r="AX2">
+        <v>6.51</v>
+      </c>
+      <c r="AY2">
         <v>1.11</v>
       </c>
-      <c r="AP2">
+      <c r="AZ2">
         <v>3</v>
       </c>
-      <c r="AQ2">
-        <v>1.88</v>
-      </c>
-      <c r="AR2">
-        <v>1.02</v>
-      </c>
-      <c r="AS2">
-        <v>7.45</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0.92</v>
+      <c r="BA2">
+        <v>1.93</v>
+      </c>
+      <c r="BB2">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="BC2">
+        <v>1.19</v>
+      </c>
+      <c r="BD2">
+        <v>0</v>
+      </c>
+      <c r="BE2">
+        <v>0</v>
+      </c>
+      <c r="BF2">
+        <v>0.9399999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:48">
+    <row r="3" spans="1:58">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C3">
-        <v>46.4</v>
+        <v>49.92</v>
       </c>
       <c r="D3">
-        <v>44.58</v>
+        <v>46.55</v>
       </c>
       <c r="E3">
-        <v>1.82</v>
+        <v>3.38</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I3">
-        <v>51</v>
+        <v>51.75</v>
       </c>
       <c r="J3">
-        <v>49</v>
+        <v>48.25</v>
       </c>
       <c r="K3">
-        <v>2.01</v>
+        <v>3.5</v>
       </c>
       <c r="L3">
-        <v>-2.04</v>
+        <v>-0.47</v>
       </c>
       <c r="M3">
-        <v>-0.03</v>
+        <v>3.03</v>
       </c>
       <c r="N3">
-        <v>-0.03</v>
+        <v>3.03</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -923,144 +1037,162 @@
         <v>1</v>
       </c>
       <c r="Q3">
-        <v>49.98</v>
+        <v>51.51</v>
       </c>
       <c r="R3">
-        <v>50.02</v>
+        <v>48.49</v>
       </c>
       <c r="S3">
-        <v>-2.04</v>
+        <v>-0.47</v>
       </c>
       <c r="T3">
-        <v>-0.03</v>
+        <v>3.03</v>
       </c>
       <c r="U3">
-        <v>-0.03</v>
+        <v>3.03</v>
       </c>
       <c r="V3">
-        <v>49.8</v>
+        <v>68.7</v>
       </c>
       <c r="W3">
-        <v>50.2</v>
+        <v>31.3</v>
       </c>
       <c r="X3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="Y3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="Z3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC3">
+        <v>68.7</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE3">
+        <v>7.27</v>
+      </c>
+      <c r="AF3">
+        <v>0.34</v>
+      </c>
+      <c r="AG3">
+        <v>2.9</v>
+      </c>
+      <c r="AH3">
+        <v>2.56</v>
+      </c>
+      <c r="AI3">
+        <v>3.24</v>
+      </c>
+      <c r="AJ3">
+        <v>2.9</v>
+      </c>
+      <c r="AK3">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="s">
+        <v>78</v>
+      </c>
+      <c r="AM3">
+        <v>-5</v>
+      </c>
+      <c r="AN3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AR3">
+        <v>8.027335204854857</v>
+      </c>
+      <c r="AT3">
+        <v>8.027335204854857</v>
+      </c>
+      <c r="AU3">
+        <v>2.006833801213714</v>
+      </c>
+      <c r="AV3">
+        <v>4.15</v>
+      </c>
+      <c r="AW3">
+        <v>5.39</v>
+      </c>
+      <c r="AX3">
+        <v>6.21</v>
+      </c>
+      <c r="AY3">
+        <v>1.11</v>
+      </c>
+      <c r="AZ3">
+        <v>4</v>
+      </c>
+      <c r="BA3">
+        <v>2.8</v>
+      </c>
+      <c r="BB3">
+        <v>0.17</v>
+      </c>
+      <c r="BC3">
+        <v>2.96</v>
+      </c>
+      <c r="BD3">
+        <v>17.49</v>
+      </c>
+      <c r="BE3">
+        <v>0</v>
+      </c>
+      <c r="BF3">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:58">
+      <c r="A4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" t="s">
         <v>65</v>
       </c>
-      <c r="AA3" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB3" t="s">
+      <c r="C4">
+        <v>49.4</v>
+      </c>
+      <c r="D4">
+        <v>47.7</v>
+      </c>
+      <c r="E4">
+        <v>1.7</v>
+      </c>
+      <c r="F4" t="s">
         <v>67</v>
       </c>
-      <c r="AC3">
-        <v>50.2</v>
-      </c>
-      <c r="AD3" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE3">
-        <v>4.93</v>
-      </c>
-      <c r="AF3">
-        <v>0.92</v>
-      </c>
-      <c r="AG3">
-        <v>2.53</v>
-      </c>
-      <c r="AH3">
-        <v>1.61</v>
-      </c>
-      <c r="AI3">
-        <v>3.46</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.92</v>
-      </c>
-      <c r="AK3">
-        <v>0</v>
-      </c>
-      <c r="AL3">
-        <v>4.72</v>
-      </c>
-      <c r="AM3">
-        <v>5.25</v>
-      </c>
-      <c r="AN3">
-        <v>6.09</v>
-      </c>
-      <c r="AO3">
-        <v>1.11</v>
-      </c>
-      <c r="AP3">
-        <v>3</v>
-      </c>
-      <c r="AQ3">
-        <v>1.93</v>
-      </c>
-      <c r="AR3">
-        <v>-0.6899999999999999</v>
-      </c>
-      <c r="AS3">
-        <v>1.19</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0.9399999999999999</v>
-      </c>
-    </row>
-    <row r="4" spans="1:48">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C4">
-        <v>48.55</v>
-      </c>
-      <c r="D4">
-        <v>47.48</v>
-      </c>
-      <c r="E4">
-        <v>1.08</v>
-      </c>
-      <c r="F4" t="s">
-        <v>56</v>
-      </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="H4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I4">
-        <v>50.56</v>
+        <v>50.88</v>
       </c>
       <c r="J4">
-        <v>49.44</v>
+        <v>49.12</v>
       </c>
       <c r="K4">
-        <v>1.12</v>
+        <v>1.75</v>
       </c>
       <c r="L4">
-        <v>-2.28</v>
+        <v>-0.5</v>
       </c>
       <c r="M4">
-        <v>-1.16</v>
+        <v>1.25</v>
       </c>
       <c r="N4">
-        <v>-1.16</v>
+        <v>1.25</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -1069,144 +1201,174 @@
         <v>1</v>
       </c>
       <c r="Q4">
-        <v>49.42</v>
+        <v>50.63</v>
       </c>
       <c r="R4">
-        <v>50.58</v>
+        <v>49.37</v>
       </c>
       <c r="S4">
-        <v>-2.28</v>
+        <v>-0.5</v>
       </c>
       <c r="T4">
-        <v>-1.16</v>
+        <v>1.25</v>
       </c>
       <c r="U4">
-        <v>-1.16</v>
+        <v>1.25</v>
       </c>
       <c r="V4">
-        <v>41.73</v>
+        <v>56.37</v>
       </c>
       <c r="W4">
-        <v>58.27</v>
+        <v>43.63</v>
       </c>
       <c r="X4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>64</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC4">
+        <v>56.37</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE4">
+        <v>7.27</v>
+      </c>
+      <c r="AF4">
+        <v>0.34</v>
+      </c>
+      <c r="AG4">
+        <v>2.9</v>
+      </c>
+      <c r="AH4">
+        <v>2.56</v>
+      </c>
+      <c r="AI4">
+        <v>3.24</v>
+      </c>
+      <c r="AJ4">
+        <v>2.9</v>
+      </c>
+      <c r="AK4">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM4">
+        <v>4</v>
+      </c>
+      <c r="AN4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP4">
+        <v>0.5097999999999999</v>
+      </c>
+      <c r="AQ4">
+        <v>-1.95999999999998</v>
+      </c>
+      <c r="AR4">
+        <v>2.74770982501213</v>
+      </c>
+      <c r="AS4">
+        <v>3.212290174987849</v>
+      </c>
+      <c r="AT4">
+        <v>2.97999999999999</v>
+      </c>
+      <c r="AU4">
+        <v>0.7449999999999974</v>
+      </c>
+      <c r="AV4">
+        <v>6.17</v>
+      </c>
+      <c r="AW4">
+        <v>7.17</v>
+      </c>
+      <c r="AX4">
+        <v>7.8</v>
+      </c>
+      <c r="AY4">
+        <v>1.11</v>
+      </c>
+      <c r="AZ4">
+        <v>3</v>
+      </c>
+      <c r="BA4">
+        <v>1.88</v>
+      </c>
+      <c r="BB4">
+        <v>1.02</v>
+      </c>
+      <c r="BC4">
+        <v>7.45</v>
+      </c>
+      <c r="BD4">
+        <v>0</v>
+      </c>
+      <c r="BE4">
+        <v>0</v>
+      </c>
+      <c r="BF4">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:58">
+      <c r="A5" t="s">
         <v>61</v>
       </c>
-      <c r="Y4" t="s">
-        <v>54</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AA4" t="s">
-        <v>55</v>
-      </c>
-      <c r="AB4" t="s">
-        <v>64</v>
-      </c>
-      <c r="AC4">
-        <v>41.73</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE4">
-        <v>4.93</v>
-      </c>
-      <c r="AF4">
-        <v>0.92</v>
-      </c>
-      <c r="AG4">
-        <v>2.53</v>
-      </c>
-      <c r="AH4">
-        <v>1.61</v>
-      </c>
-      <c r="AI4">
-        <v>3.46</v>
-      </c>
-      <c r="AJ4">
-        <v>2.53</v>
-      </c>
-      <c r="AK4">
-        <v>0</v>
-      </c>
-      <c r="AL4">
-        <v>4.15</v>
-      </c>
-      <c r="AM4">
-        <v>4.61</v>
-      </c>
-      <c r="AN4">
-        <v>5.55</v>
-      </c>
-      <c r="AO4">
-        <v>1.11</v>
-      </c>
-      <c r="AP4">
-        <v>4</v>
-      </c>
-      <c r="AQ4">
-        <v>2.8</v>
-      </c>
-      <c r="AR4">
-        <v>0.17</v>
-      </c>
-      <c r="AS4">
-        <v>2.96</v>
-      </c>
-      <c r="AT4">
-        <v>17.49</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:48">
-      <c r="A5" t="s">
-        <v>51</v>
-      </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C5">
-        <v>47.68</v>
+        <v>50</v>
       </c>
       <c r="D5">
-        <v>49.02</v>
+        <v>48.52</v>
       </c>
       <c r="E5">
-        <v>-1.35</v>
+        <v>1.48</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="H5" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="I5">
-        <v>49.3</v>
+        <v>50.75</v>
       </c>
       <c r="J5">
-        <v>50.7</v>
+        <v>49.25</v>
       </c>
       <c r="K5">
-        <v>-1.4</v>
+        <v>1.5</v>
       </c>
       <c r="L5">
-        <v>-1.84</v>
+        <v>0.19</v>
       </c>
       <c r="M5">
-        <v>-3.24</v>
+        <v>1.69</v>
       </c>
       <c r="N5">
-        <v>-3.24</v>
+        <v>1.69</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -1215,144 +1377,174 @@
         <v>1</v>
       </c>
       <c r="Q5">
-        <v>48.38</v>
+        <v>50.32</v>
       </c>
       <c r="R5">
-        <v>51.62</v>
+        <v>49.68</v>
       </c>
       <c r="S5">
-        <v>-1.84</v>
+        <v>0.19</v>
       </c>
       <c r="T5">
-        <v>-3.24</v>
+        <v>1.69</v>
       </c>
       <c r="U5">
-        <v>-3.24</v>
+        <v>0.64</v>
       </c>
       <c r="V5">
-        <v>32.31</v>
+        <v>53.53</v>
       </c>
       <c r="W5">
-        <v>67.69</v>
+        <v>46.47</v>
       </c>
       <c r="X5" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="Y5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="Z5" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AA5" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AB5" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AC5">
-        <v>32.31</v>
+        <v>53.53</v>
       </c>
       <c r="AD5" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="AE5">
-        <v>4.93</v>
+        <v>7.27</v>
       </c>
       <c r="AF5">
-        <v>0.92</v>
+        <v>0.34</v>
       </c>
       <c r="AG5">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="AH5">
-        <v>1.61</v>
+        <v>2.56</v>
       </c>
       <c r="AI5">
-        <v>3.46</v>
+        <v>3.24</v>
       </c>
       <c r="AJ5">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="AK5">
         <v>0</v>
       </c>
-      <c r="AL5">
-        <v>5.7</v>
+      <c r="AL5" t="s">
+        <v>80</v>
       </c>
       <c r="AM5">
-        <v>6.34</v>
-      </c>
-      <c r="AN5">
-        <v>7.05</v>
-      </c>
-      <c r="AO5">
+        <v>-6</v>
+      </c>
+      <c r="AN5" t="s">
+        <v>84</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP5">
+        <v>0.539</v>
+      </c>
+      <c r="AQ5">
+        <v>-7.800000000000011</v>
+      </c>
+      <c r="AR5">
+        <v>7.686016982113116</v>
+      </c>
+      <c r="AS5">
+        <v>9.486016982113126</v>
+      </c>
+      <c r="AT5">
+        <v>8.58601698211312</v>
+      </c>
+      <c r="AU5">
+        <v>2.14650424552828</v>
+      </c>
+      <c r="AV5">
+        <v>5.31</v>
+      </c>
+      <c r="AW5">
+        <v>6.57</v>
+      </c>
+      <c r="AX5">
+        <v>7.26</v>
+      </c>
+      <c r="AY5">
         <v>1.11</v>
       </c>
-      <c r="AP5">
+      <c r="AZ5">
         <v>3</v>
       </c>
-      <c r="AQ5">
-        <v>2.19</v>
-      </c>
-      <c r="AR5">
-        <v>-2.89</v>
-      </c>
-      <c r="AS5">
-        <v>6.84</v>
-      </c>
-      <c r="AT5">
-        <v>30.49</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>0.95</v>
+      <c r="BA5">
+        <v>1.54</v>
+      </c>
+      <c r="BB5">
+        <v>-4.01</v>
+      </c>
+      <c r="BC5">
+        <v>11.42</v>
+      </c>
+      <c r="BD5">
+        <v>42.06</v>
+      </c>
+      <c r="BE5">
+        <v>23.64</v>
+      </c>
+      <c r="BF5">
+        <v>0.6899999999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:48">
+    <row r="6" spans="1:58">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="C6">
-        <v>47.52</v>
+        <v>47.32</v>
       </c>
       <c r="D6">
-        <v>48.48</v>
+        <v>45.6</v>
       </c>
       <c r="E6">
-        <v>-0.95</v>
+        <v>1.72</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H6" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I6">
-        <v>49.51</v>
+        <v>50.93</v>
       </c>
       <c r="J6">
-        <v>50.49</v>
+        <v>49.07</v>
       </c>
       <c r="K6">
-        <v>-0.99</v>
+        <v>1.86</v>
       </c>
       <c r="L6">
-        <v>-2.3</v>
+        <v>-2.64</v>
       </c>
       <c r="M6">
-        <v>-3.28</v>
+        <v>-0.78</v>
       </c>
       <c r="N6">
-        <v>-3.28</v>
+        <v>-0.78</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -1361,144 +1553,174 @@
         <v>1</v>
       </c>
       <c r="Q6">
-        <v>48.36</v>
+        <v>49.61</v>
       </c>
       <c r="R6">
-        <v>51.64</v>
+        <v>50.39</v>
       </c>
       <c r="S6">
-        <v>-2.3</v>
+        <v>-2.64</v>
       </c>
       <c r="T6">
-        <v>-3.28</v>
+        <v>-0.78</v>
       </c>
       <c r="U6">
-        <v>-3.28</v>
+        <v>-0.78</v>
       </c>
       <c r="V6">
-        <v>31.11</v>
+        <v>44.91</v>
       </c>
       <c r="W6">
-        <v>68.89</v>
+        <v>55.09</v>
       </c>
       <c r="X6" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="Y6" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="Z6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="AA6" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="AB6" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="AC6">
-        <v>31.11</v>
+        <v>44.91</v>
       </c>
       <c r="AD6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE6">
+        <v>7.27</v>
+      </c>
+      <c r="AF6">
+        <v>0.34</v>
+      </c>
+      <c r="AG6">
+        <v>2.9</v>
+      </c>
+      <c r="AH6">
+        <v>2.56</v>
+      </c>
+      <c r="AI6">
+        <v>3.24</v>
+      </c>
+      <c r="AJ6">
+        <v>2.9</v>
+      </c>
+      <c r="AK6">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="s">
+        <v>80</v>
+      </c>
+      <c r="AM6">
+        <v>-6</v>
+      </c>
+      <c r="AN6" t="s">
+        <v>85</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP6">
+        <v>0.5351</v>
+      </c>
+      <c r="AQ6">
+        <v>-7.02000000000001</v>
+      </c>
+      <c r="AR6">
+        <v>5.215620294959367</v>
+      </c>
+      <c r="AS6">
+        <v>6.235620294959377</v>
+      </c>
+      <c r="AT6">
+        <v>5.725620294959372</v>
+      </c>
+      <c r="AU6">
+        <v>1.431405073739843</v>
+      </c>
+      <c r="AV6">
+        <v>4.14</v>
+      </c>
+      <c r="AW6">
+        <v>5.29</v>
+      </c>
+      <c r="AX6">
+        <v>6.13</v>
+      </c>
+      <c r="AY6">
+        <v>1.11</v>
+      </c>
+      <c r="AZ6">
+        <v>3</v>
+      </c>
+      <c r="BA6">
+        <v>1.93</v>
+      </c>
+      <c r="BB6">
+        <v>1.35</v>
+      </c>
+      <c r="BC6">
+        <v>5.75</v>
+      </c>
+      <c r="BD6">
+        <v>0</v>
+      </c>
+      <c r="BE6">
+        <v>0</v>
+      </c>
+      <c r="BF6">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:58">
+      <c r="A7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C7">
+        <v>46.05</v>
+      </c>
+      <c r="D7">
+        <v>48.32</v>
+      </c>
+      <c r="E7">
+        <v>-2.28</v>
+      </c>
+      <c r="F7" t="s">
         <v>68</v>
       </c>
-      <c r="AE6">
-        <v>4.93</v>
-      </c>
-      <c r="AF6">
-        <v>0.92</v>
-      </c>
-      <c r="AG6">
-        <v>2.53</v>
-      </c>
-      <c r="AH6">
-        <v>1.61</v>
-      </c>
-      <c r="AI6">
-        <v>3.46</v>
-      </c>
-      <c r="AJ6">
-        <v>2.53</v>
-      </c>
-      <c r="AK6">
-        <v>0</v>
-      </c>
-      <c r="AL6">
-        <v>5.31</v>
-      </c>
-      <c r="AM6">
-        <v>5.9</v>
-      </c>
-      <c r="AN6">
-        <v>6.67</v>
-      </c>
-      <c r="AO6">
-        <v>1.11</v>
-      </c>
-      <c r="AP6">
-        <v>3</v>
-      </c>
-      <c r="AQ6">
-        <v>1.54</v>
-      </c>
-      <c r="AR6">
-        <v>-4.01</v>
-      </c>
-      <c r="AS6">
-        <v>11.42</v>
-      </c>
-      <c r="AT6">
-        <v>42.06</v>
-      </c>
-      <c r="AU6">
-        <v>23.64</v>
-      </c>
-      <c r="AV6">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:48">
-      <c r="A7" t="s">
-        <v>53</v>
-      </c>
-      <c r="B7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C7">
-        <v>47.1</v>
-      </c>
-      <c r="D7">
-        <v>47.95</v>
-      </c>
-      <c r="E7">
-        <v>-0.85</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H7" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I7">
-        <v>49.55</v>
+        <v>48.79</v>
       </c>
       <c r="J7">
-        <v>50.45</v>
+        <v>51.21</v>
       </c>
       <c r="K7">
-        <v>-0.89</v>
+        <v>-2.41</v>
       </c>
       <c r="L7">
-        <v>-2.81</v>
+        <v>-1.72</v>
       </c>
       <c r="M7">
-        <v>-3.7</v>
+        <v>-4.13</v>
       </c>
       <c r="N7">
-        <v>-3.7</v>
+        <v>-4.13</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -1507,100 +1729,130 @@
         <v>1</v>
       </c>
       <c r="Q7">
-        <v>48.15</v>
+        <v>47.93</v>
       </c>
       <c r="R7">
-        <v>51.85</v>
+        <v>52.07</v>
       </c>
       <c r="S7">
-        <v>-2.81</v>
+        <v>-1.72</v>
       </c>
       <c r="T7">
-        <v>-3.7</v>
+        <v>-4.13</v>
       </c>
       <c r="U7">
-        <v>-3.7</v>
+        <v>-4.13</v>
       </c>
       <c r="V7">
-        <v>25.22</v>
+        <v>28.76</v>
       </c>
       <c r="W7">
-        <v>74.78</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="X7" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="Y7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="Z7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="AA7" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="AB7" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="AC7">
-        <v>25.22</v>
+        <v>28.76</v>
       </c>
       <c r="AD7" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="AE7">
-        <v>4.93</v>
+        <v>7.27</v>
       </c>
       <c r="AF7">
-        <v>0.92</v>
+        <v>0.34</v>
       </c>
       <c r="AG7">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="AH7">
-        <v>1.61</v>
+        <v>2.56</v>
       </c>
       <c r="AI7">
-        <v>3.46</v>
+        <v>3.24</v>
       </c>
       <c r="AJ7">
-        <v>2.53</v>
+        <v>2.9</v>
       </c>
       <c r="AK7">
         <v>0</v>
       </c>
-      <c r="AL7">
-        <v>4.14</v>
+      <c r="AL7" t="s">
+        <v>80</v>
       </c>
       <c r="AM7">
-        <v>4.6</v>
-      </c>
-      <c r="AN7">
-        <v>5.55</v>
-      </c>
-      <c r="AO7">
+        <v>-6</v>
+      </c>
+      <c r="AN7" t="s">
+        <v>86</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AP7">
+        <v>0.5174</v>
+      </c>
+      <c r="AQ7">
+        <v>-3.47999999999999</v>
+      </c>
+      <c r="AR7">
+        <v>1.86896365369746</v>
+      </c>
+      <c r="AS7">
+        <v>0.6510363463025506</v>
+      </c>
+      <c r="AT7">
+        <v>1.260000000000005</v>
+      </c>
+      <c r="AU7">
+        <v>0.3150000000000013</v>
+      </c>
+      <c r="AV7">
+        <v>5.7</v>
+      </c>
+      <c r="AW7">
+        <v>6.69</v>
+      </c>
+      <c r="AX7">
+        <v>7.37</v>
+      </c>
+      <c r="AY7">
         <v>1.11</v>
       </c>
-      <c r="AP7">
+      <c r="AZ7">
         <v>3</v>
       </c>
-      <c r="AQ7">
-        <v>1.93</v>
-      </c>
-      <c r="AR7">
-        <v>1.35</v>
-      </c>
-      <c r="AS7">
-        <v>5.75</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0.9399999999999999</v>
+      <c r="BA7">
+        <v>2.19</v>
+      </c>
+      <c r="BB7">
+        <v>-2.89</v>
+      </c>
+      <c r="BC7">
+        <v>6.84</v>
+      </c>
+      <c r="BD7">
+        <v>30.49</v>
+      </c>
+      <c r="BE7">
+        <v>0</v>
+      </c>
+      <c r="BF7">
+        <v>0.95</v>
       </c>
     </row>
   </sheetData>
